--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -468,7 +468,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0</t>
   </si>
   <si>
     <t>Practitioner.meta.security</t>
@@ -636,7 +636,7 @@
     <t>specialty</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-specialty|2.2.0}
 </t>
   </si>
   <si>
@@ -756,7 +756,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-identifier-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1000,7 +1000,7 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0-ballot-2}
+    <t xml:space="preserve">HumanName {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-human-name|2.2.0}
 </t>
   </si>
   <si>
@@ -1243,7 +1243,7 @@
     <t>Practitioner.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0-ballot-2}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1271,7 +1271,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0-ballot-2}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -2071,7 +2071,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.03515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
